--- a/07-opportunities-solutions/riesgos-solucion-propuesta.xlsx
+++ b/07-opportunities-solutions/riesgos-solucion-propuesta.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="STRIDE_Cliente" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Riesgos_Solucion_Propuesta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -554,7 +554,7 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="3" ht="70" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="4" ht="70" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="5" ht="70" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="6" ht="70" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="7" ht="70" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
     <row r="8" ht="70" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
